--- a/Price Tracker Sheet.xlsx
+++ b/Price Tracker Sheet.xlsx
@@ -2,125 +2,114 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://acushnetco-my.sharepoint.com/personal/tim_snow_acushnetgolf_com/Documents/16_Claude/Github/Price Tracker/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="13" documentId="8_{05A1E0DB-2DB4-194D-9FCF-25B59FC7ADE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{24A4BB4E-2E04-D347-96B9-7EDDFBFA0A9B}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1D0D37F5-6779-024E-836C-8AB1A09B55F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1500" yWindow="1320" windowWidth="27640" windowHeight="16940" activeTab="1" xr2:uid="{F8BB35C5-DD24-994E-A41E-515D9CE3105B}"/>
+    <workbookView xWindow="1500" yWindow="800" windowWidth="27640" windowHeight="16940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Where to find price" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="181029" iterateDelta="1E-4"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="0" iterateDelta="1E-4"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="33">
+  <si>
+    <t>Category</t>
+  </si>
   <si>
     <t>Brand</t>
   </si>
   <si>
-    <t>Category</t>
+    <t>Product Name</t>
+  </si>
+  <si>
+    <t>Retailer</t>
+  </si>
+  <si>
+    <t>URL</t>
+  </si>
+  <si>
+    <t>RRP</t>
+  </si>
+  <si>
+    <t>Premium Performance Spikeless</t>
+  </si>
+  <si>
+    <t>Ecco</t>
+  </si>
+  <si>
+    <t>Biom C5 BOA</t>
+  </si>
+  <si>
+    <t>Golf Box</t>
+  </si>
+  <si>
+    <t>https://www.golfbox.com.au/shoes/ecco-m-biom-h5-boa-golf-shoes-white/black/</t>
+  </si>
+  <si>
+    <t>UA</t>
+  </si>
+  <si>
+    <t>Drive Pro Clon SL</t>
+  </si>
+  <si>
+    <t>https://www.golfbox.com.au/shoes/under-armour-drive-pro-clone-sl-golf-shoes-black/anthracite/</t>
+  </si>
+  <si>
+    <t>FootJoy</t>
+  </si>
+  <si>
+    <t>Pro/SL</t>
+  </si>
+  <si>
+    <t>https://www.golfbox.com.au/shoes/footjoy-pro-sl-golf-shoes-white/blue/red/</t>
   </si>
   <si>
     <t>Adidas</t>
   </si>
   <si>
-    <t>Retailer</t>
-  </si>
-  <si>
-    <t>URL</t>
-  </si>
-  <si>
-    <t>https://www.golfbox.com.au/shoes/ecco-m-biom-h5-boa-golf-shoes-white/black/</t>
-  </si>
-  <si>
-    <t>Product Name</t>
-  </si>
-  <si>
-    <t>Ecco</t>
-  </si>
-  <si>
-    <t>Premium Performance Spikeless</t>
-  </si>
-  <si>
-    <t>Biom C5 BOA</t>
-  </si>
-  <si>
-    <t>https://www.golfbox.com.au/shoes/under-armour-drive-pro-clone-sl-golf-shoes-black/anthracite/</t>
-  </si>
-  <si>
-    <t>UA</t>
-  </si>
-  <si>
-    <t>Drive Pro Clon SL</t>
-  </si>
-  <si>
-    <t>Golf Box</t>
-  </si>
-  <si>
-    <t>https://www.golfbox.com.au/shoes/footjoy-pro-sl-golf-shoes-white/blue/red/</t>
-  </si>
-  <si>
-    <t>FootJoy</t>
-  </si>
-  <si>
-    <t>Pro/SL</t>
-  </si>
-  <si>
     <t>Adizero ZG Spikeless</t>
   </si>
   <si>
     <t>https://www.golfbox.com.au/shoes/adidas-adizero-zg-spikeless-golf-shoes-ftwr-white/core-black/ice-tangerine/</t>
   </si>
   <si>
-    <t>https://www.footjoy.com.au/en_AU/men/shoes/spikeless/prosl/017PSL.html?dwvar_017PSL_color=56949</t>
+    <t>On Course</t>
   </si>
   <si>
     <t>https://oncoursegolf.com.au/adidas/Adidas-Adizero-ZG-Spikeless-Golf-Shoes</t>
   </si>
   <si>
-    <t>On Course</t>
-  </si>
-  <si>
     <t>https://oncoursegolf.com.au/Ecco/ECCO-Biom-H5-BOA-Golf-Shoes-Black</t>
   </si>
   <si>
     <t>Performance Spikeless</t>
   </si>
   <si>
+    <t>Fuel</t>
+  </si>
+  <si>
     <t>https://oncoursegolf.com.au/FootJoy/Footjoy-Fuel-White-Black-Coral</t>
   </si>
   <si>
-    <t>Fuel</t>
-  </si>
-  <si>
     <t>https://www.footjoy.com.au/en_AU/men/shoes/spikeless/fuel/008FJF.html?dwvar_008FJF_color=55417</t>
   </si>
   <si>
     <t>Example page source with price location</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            "priceCurrency": "AUD",
+                "price": "159.99",
+            "itemCondition" : "https://schema.org/NewCondition",</t>
   </si>
   <si>
     <t>&lt;div class="product-price"&gt;
@@ -134,21 +123,32 @@
             "itemCondition" : "https://schema.org/NewCondition",</t>
   </si>
   <si>
-    <t xml:space="preserve">            "priceCurrency": "AUD",
-                "price": "159.99",
-            "itemCondition" : "https://schema.org/NewCondition",</t>
+    <t>Traditions</t>
+  </si>
+  <si>
+    <t>https://oncoursegolf.com.au/FootJoy/FootJoy-Traditions-Blucher-White</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <numFmts count="2">
+    <numFmt numFmtId="8" formatCode="&quot;$&quot;#,##0.00_);[Red]\(&quot;$&quot;#,##0.00\)"/>
+    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
+  </numFmts>
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -178,12 +178,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -517,25 +520,26 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2F65DE6-775C-344B-9174-9F182DA2B672}">
-  <dimension ref="A1:E10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="23.83203125" customWidth="1"/>
     <col min="2" max="3" width="15.1640625" customWidth="1"/>
     <col min="4" max="4" width="30.5" customWidth="1"/>
-    <col min="5" max="5" width="68.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="87" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
       <c r="C1" s="1" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>3</v>
@@ -543,27 +547,33 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
       </c>
       <c r="C2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" t="s">
         <v>9</v>
       </c>
-      <c r="D2" t="s">
-        <v>13</v>
-      </c>
       <c r="E2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+        <v>10</v>
+      </c>
+      <c r="F2" s="3">
+        <v>399.95</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B3" t="s">
         <v>11</v>
@@ -572,129 +582,153 @@
         <v>12</v>
       </c>
       <c r="D3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" t="s">
         <v>13</v>
       </c>
-      <c r="E3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F3" s="5">
+        <v>289.99</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F4" s="3">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" t="s">
+        <v>19</v>
+      </c>
+      <c r="F5">
+        <v>289.99</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F6">
+        <v>289.99</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" t="s">
         <v>8</v>
       </c>
-      <c r="B4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D4" t="s">
-        <v>13</v>
-      </c>
-      <c r="E4" t="s">
+      <c r="D7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F7" s="3">
+        <v>399.95</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C5" t="s">
-        <v>17</v>
-      </c>
-      <c r="D5" t="s">
-        <v>13</v>
-      </c>
-      <c r="E5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C6" t="s">
-        <v>16</v>
-      </c>
-      <c r="D6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E6" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E7" t="s">
+      <c r="C8" t="s">
+        <v>24</v>
+      </c>
+      <c r="D8" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C8" t="s">
-        <v>9</v>
-      </c>
-      <c r="D8" t="s">
-        <v>21</v>
-      </c>
       <c r="E8" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+        <v>25</v>
+      </c>
+      <c r="F8" s="3">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>23</v>
       </c>
       <c r="B9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D9" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="E9" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
+        <v>26</v>
+      </c>
+      <c r="F9" s="3">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A10" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B10" t="s">
-        <v>15</v>
-      </c>
-      <c r="C10" t="s">
-        <v>25</v>
-      </c>
-      <c r="D10" t="s">
-        <v>15</v>
-      </c>
-      <c r="E10" t="s">
-        <v>26</v>
+      <c r="B10" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="F10" s="3">
+        <v>249</v>
       </c>
     </row>
   </sheetData>
@@ -703,7 +737,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6FB2654-6ECD-5947-9B5C-3C897F1BC8C0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A4:B19"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
@@ -720,26 +754,26 @@
     </row>
     <row r="5" spans="1:2" ht="122" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="122" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="122" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="122" customHeight="1" x14ac:dyDescent="0.2"/>

--- a/Price Tracker Sheet.xlsx
+++ b/Price Tracker Sheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://acushnetco-my.sharepoint.com/personal/tim_snow_acushnetgolf_com/Documents/16_Claude/Github/Price Tracker/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1D0D37F5-6779-024E-836C-8AB1A09B55F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="8_{1D0D37F5-6779-024E-836C-8AB1A09B55F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{80E0F856-17E4-A845-B194-EF3624C71BCC}"/>
   <bookViews>
     <workbookView xWindow="1500" yWindow="800" windowWidth="27640" windowHeight="16940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="32">
   <si>
     <t>Category</t>
   </si>
@@ -99,9 +99,6 @@
   </si>
   <si>
     <t>https://oncoursegolf.com.au/FootJoy/Footjoy-Fuel-White-Black-Coral</t>
-  </si>
-  <si>
-    <t>https://www.footjoy.com.au/en_AU/men/shoes/spikeless/fuel/008FJF.html?dwvar_008FJF_color=55417</t>
   </si>
   <si>
     <t>Example page source with price location</t>
@@ -521,7 +518,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="23.83203125" customWidth="1"/>
@@ -692,42 +689,22 @@
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
+      <c r="A9" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="C9" t="s">
-        <v>24</v>
-      </c>
-      <c r="D9" t="s">
-        <v>14</v>
-      </c>
-      <c r="E9" t="s">
-        <v>26</v>
+      <c r="C9" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>31</v>
       </c>
       <c r="F9" s="3">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A10" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="F10" s="3">
         <v>249</v>
       </c>
     </row>
@@ -749,7 +726,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="122" customHeight="1" x14ac:dyDescent="0.2">
@@ -757,7 +734,7 @@
         <v>9</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="122" customHeight="1" x14ac:dyDescent="0.2">
@@ -765,7 +742,7 @@
         <v>14</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="122" customHeight="1" x14ac:dyDescent="0.2">
@@ -773,7 +750,7 @@
         <v>20</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="122" customHeight="1" x14ac:dyDescent="0.2"/>

--- a/Price Tracker Sheet.xlsx
+++ b/Price Tracker Sheet.xlsx
@@ -8,20 +8,20 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://acushnetco-my.sharepoint.com/personal/tim_snow_acushnetgolf_com/Documents/16_Claude/Github/Price Tracker/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1D0D37F5-6779-024E-836C-8AB1A09B55F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="8_{1D0D37F5-6779-024E-836C-8AB1A09B55F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{49D0FE70-649C-5E4A-972C-A9845A1ED673}"/>
   <bookViews>
-    <workbookView xWindow="1500" yWindow="800" windowWidth="27640" windowHeight="16940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-25420" yWindow="-27640" windowWidth="27640" windowHeight="16940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Where to find price" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0" iterateDelta="1E-4"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="32">
   <si>
     <t>Category</t>
   </si>
@@ -99,9 +99,6 @@
   </si>
   <si>
     <t>https://oncoursegolf.com.au/FootJoy/Footjoy-Fuel-White-Black-Coral</t>
-  </si>
-  <si>
-    <t>https://www.footjoy.com.au/en_AU/men/shoes/spikeless/fuel/008FJF.html?dwvar_008FJF_color=55417</t>
   </si>
   <si>
     <t>Example page source with price location</t>
@@ -137,7 +134,7 @@
     <numFmt numFmtId="8" formatCode="&quot;$&quot;#,##0.00_);[Red]\(&quot;$&quot;#,##0.00\)"/>
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -149,6 +146,14 @@
       <sz val="12"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -175,10 +180,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -187,8 +193,10 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -521,7 +529,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="23.83203125" customWidth="1"/>
@@ -692,44 +700,27 @@
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
+      <c r="A9" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="C9" t="s">
-        <v>24</v>
-      </c>
-      <c r="D9" t="s">
-        <v>14</v>
-      </c>
-      <c r="E9" t="s">
-        <v>26</v>
+      <c r="C9" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>31</v>
       </c>
       <c r="F9" s="3">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A10" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="F10" s="3">
         <v>249</v>
       </c>
+    </row>
+    <row r="26" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E26" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -749,7 +740,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="122" customHeight="1" x14ac:dyDescent="0.2">
@@ -757,7 +748,7 @@
         <v>9</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="122" customHeight="1" x14ac:dyDescent="0.2">
@@ -765,7 +756,7 @@
         <v>14</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="122" customHeight="1" x14ac:dyDescent="0.2">
@@ -773,7 +764,7 @@
         <v>20</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="122" customHeight="1" x14ac:dyDescent="0.2"/>
